--- a/product_selector_out/STM8AF63.xlsx
+++ b/product_selector_out/STM8AF63.xlsx
@@ -488,7 +488,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.34375" customWidth="1" min="1" max="1"/>
@@ -523,7 +523,8 @@
     <col width="23.46484375" customWidth="1" min="30" max="30"/>
     <col width="11.6328125" customWidth="1" min="31" max="31"/>
     <col width="43.6484375" customWidth="1" min="32" max="32"/>
-    <col width="52" customWidth="1" min="33" max="33"/>
+    <col width="18" customWidth="1" min="33" max="33"/>
+    <col width="52" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -704,6 +705,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -871,6 +877,11 @@
       </c>
       <c r="AG11" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH11" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6366.pdf</t>
         </is>
       </c>
@@ -1038,14 +1049,19 @@
       </c>
       <c r="AG12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="AH12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm8af6388.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId1"/>
@@ -1062,7 +1078,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG12"/>
+  <dimension ref="A1:AH12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1098,6 +1114,7 @@
     <col width="16" customWidth="1" min="31" max="31"/>
     <col width="16" customWidth="1" min="32" max="32"/>
     <col width="16" customWidth="1" min="33" max="33"/>
+    <col width="16" customWidth="1" min="34" max="34"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1284,6 +1301,11 @@
       </c>
       <c r="AG10" s="2" t="inlineStr">
         <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
           <t>Datasheet URL</t>
         </is>
       </c>
@@ -1449,7 +1471,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG11" s="6" t="inlineStr">
+      <c r="AG11" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH11" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -1616,7 +1643,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AG12" s="6" t="inlineStr">
+      <c r="AG12" s="7" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="AH12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -1624,8 +1656,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:AG9"/>
-    <mergeCell ref="A1:AG8"/>
+    <mergeCell ref="A1:AH8"/>
+    <mergeCell ref="A9:AH9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
